--- a/Deliverables/Interface_Board/BOM/LCSC_Interface_Board-500-100.xlsx
+++ b/Deliverables/Interface_Board/BOM/LCSC_Interface_Board-500-100.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FA04E2-A0AE-4F75-B513-D4E41FE38E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="221">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -690,18 +700,24 @@
   </si>
   <si>
     <t>Alibaba</t>
+  </si>
+  <si>
+    <t>Alibaba Shipping Charges</t>
+  </si>
+  <si>
+    <t>Total Cost With Shipping</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,6 +920,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1331,7 +1355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1841,6 +1865,12 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2140,7 +2170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2169,31 +2199,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="16.5" thickBot="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="174"/>
-      <c r="O1" s="174"/>
-      <c r="P1" s="174"/>
-      <c r="Q1" s="174"/>
-      <c r="R1" s="174"/>
-      <c r="S1" s="174"/>
-      <c r="T1" s="174"/>
-      <c r="U1" s="174"/>
-      <c r="V1" s="174"/>
-      <c r="W1" s="175"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
+      <c r="P1" s="180"/>
+      <c r="Q1" s="180"/>
+      <c r="R1" s="180"/>
+      <c r="S1" s="180"/>
+      <c r="T1" s="180"/>
+      <c r="U1" s="180"/>
+      <c r="V1" s="180"/>
+      <c r="W1" s="181"/>
     </row>
     <row r="2" spans="1:39" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2286,7 +2316,7 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="178" t="s">
+      <c r="B3" s="184" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="76" t="s">
@@ -2360,7 +2390,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="179"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="80" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +2462,7 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="179"/>
+      <c r="B5" s="185"/>
       <c r="C5" s="80" t="s">
         <v>33</v>
       </c>
@@ -2504,7 +2534,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="179"/>
+      <c r="B6" s="185"/>
       <c r="C6" s="85" t="s">
         <v>40</v>
       </c>
@@ -2560,14 +2590,14 @@
         <v>3.8E-3</v>
       </c>
       <c r="T6" s="66">
-        <f t="shared" ref="T6:T31" si="3">S6*K6</f>
+        <f t="shared" ref="T6:T30" si="3">S6*K6</f>
         <v>6.08</v>
       </c>
       <c r="U6" s="66">
         <v>3.8E-3</v>
       </c>
       <c r="V6" s="66">
-        <f t="shared" ref="V6:V31" si="4">U6*L6</f>
+        <f>U6*L6</f>
         <v>12.16</v>
       </c>
       <c r="W6" s="145"/>
@@ -2576,7 +2606,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="179"/>
+      <c r="B7" s="185"/>
       <c r="C7" s="85" t="s">
         <v>47</v>
       </c>
@@ -2639,7 +2669,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
       <c r="V7" s="66">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="V7:V24" si="4">U7*L7</f>
         <v>26.840000000000003</v>
       </c>
       <c r="W7" s="145"/>
@@ -2648,7 +2678,7 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="179"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="85" t="s">
         <v>54</v>
       </c>
@@ -2720,7 +2750,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="179"/>
+      <c r="B9" s="185"/>
       <c r="C9" s="85" t="s">
         <v>61</v>
       </c>
@@ -2793,7 +2823,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="179"/>
+      <c r="B10" s="185"/>
       <c r="C10" s="85" t="s">
         <v>65</v>
       </c>
@@ -2866,7 +2896,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="179"/>
+      <c r="B11" s="185"/>
       <c r="C11" s="85" t="s">
         <v>71</v>
       </c>
@@ -2939,7 +2969,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="180"/>
+      <c r="B12" s="186"/>
       <c r="C12" s="90" t="s">
         <v>78</v>
       </c>
@@ -3012,7 +3042,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="178" t="s">
+      <c r="B13" s="184" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="96" t="s">
@@ -3087,7 +3117,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="180"/>
+      <c r="B14" s="186"/>
       <c r="C14" s="90" t="s">
         <v>93</v>
       </c>
@@ -3306,7 +3336,7 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="178" t="s">
+      <c r="B17" s="184" t="s">
         <v>111</v>
       </c>
       <c r="C17" s="106" t="s">
@@ -3381,7 +3411,7 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="179"/>
+      <c r="B18" s="185"/>
       <c r="C18" s="108" t="s">
         <v>118</v>
       </c>
@@ -3454,7 +3484,7 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="179"/>
+      <c r="B19" s="185"/>
       <c r="C19" s="108" t="s">
         <v>123</v>
       </c>
@@ -3527,7 +3557,7 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="179"/>
+      <c r="B20" s="185"/>
       <c r="C20" s="108" t="s">
         <v>128</v>
       </c>
@@ -3600,7 +3630,7 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="179"/>
+      <c r="B21" s="185"/>
       <c r="C21" s="108" t="s">
         <v>135</v>
       </c>
@@ -3673,7 +3703,7 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="179"/>
+      <c r="B22" s="185"/>
       <c r="C22" s="108" t="s">
         <v>142</v>
       </c>
@@ -3746,7 +3776,7 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="180"/>
+      <c r="B23" s="186"/>
       <c r="C23" s="110" t="s">
         <v>148</v>
       </c>
@@ -3819,7 +3849,7 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="179" t="s">
+      <c r="B24" s="185" t="s">
         <v>153</v>
       </c>
       <c r="C24" s="137" t="s">
@@ -3896,7 +3926,7 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="179"/>
+      <c r="B25" s="185"/>
       <c r="C25" s="108" t="s">
         <v>160</v>
       </c>
@@ -3959,7 +3989,7 @@
         <v>0.1716</v>
       </c>
       <c r="V25" s="66">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="V25:V31" si="5">U25*L25</f>
         <v>178.464</v>
       </c>
       <c r="W25" s="153"/>
@@ -3969,7 +3999,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="179"/>
+      <c r="B26" s="185"/>
       <c r="C26" s="160" t="s">
         <v>166</v>
       </c>
@@ -4032,7 +4062,7 @@
         <v>0.1255</v>
       </c>
       <c r="V26" s="135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130.52000000000001</v>
       </c>
       <c r="W26" s="167"/>
@@ -4042,7 +4072,7 @@
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="178" t="s">
+      <c r="B27" s="184" t="s">
         <v>173</v>
       </c>
       <c r="C27" s="111" t="s">
@@ -4090,25 +4120,25 @@
         <v>178</v>
       </c>
       <c r="Q27" s="55">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="R27" s="55">
         <f>Q27*100</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S27" s="55">
-        <v>0.37540000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="T27" s="129">
         <f t="shared" si="3"/>
-        <v>225.24</v>
+        <v>210</v>
       </c>
       <c r="U27" s="73">
-        <v>0.372681818181818</v>
+        <v>0.35</v>
       </c>
       <c r="V27" s="129">
-        <f t="shared" si="4"/>
-        <v>409.94999999999982</v>
+        <f t="shared" si="5"/>
+        <v>385</v>
       </c>
       <c r="W27" s="156" t="s">
         <v>179</v>
@@ -4119,7 +4149,7 @@
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="179"/>
+      <c r="B28" s="185"/>
       <c r="C28" s="113" t="s">
         <v>180</v>
       </c>
@@ -4182,7 +4212,7 @@
         <v>0.75</v>
       </c>
       <c r="V28" s="66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1575</v>
       </c>
       <c r="W28" s="157"/>
@@ -4192,7 +4222,7 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="179"/>
+      <c r="B29" s="185"/>
       <c r="C29" s="113" t="s">
         <v>186</v>
       </c>
@@ -4238,25 +4268,25 @@
         <v>178</v>
       </c>
       <c r="Q29" s="61">
-        <v>0.56399999999999995</v>
+        <v>0.18</v>
       </c>
       <c r="R29" s="60">
         <f>Q29*L29</f>
-        <v>592.19999999999993</v>
+        <v>189</v>
       </c>
       <c r="S29" s="60">
-        <v>0.26961538461538398</v>
+        <v>0.18</v>
       </c>
       <c r="T29" s="66">
         <f t="shared" si="3"/>
-        <v>140.19999999999968</v>
+        <v>93.6</v>
       </c>
       <c r="U29" s="61">
-        <v>0.24994285714285699</v>
+        <v>0.18</v>
       </c>
       <c r="V29" s="66">
-        <f t="shared" si="4"/>
-        <v>262.43999999999983</v>
+        <f t="shared" si="5"/>
+        <v>189</v>
       </c>
       <c r="W29" s="157"/>
       <c r="X29" s="67"/>
@@ -4265,7 +4295,7 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="179"/>
+      <c r="B30" s="185"/>
       <c r="C30" s="26" t="s">
         <v>189</v>
       </c>
@@ -4328,7 +4358,7 @@
         <v>1.8200000000000001E-2</v>
       </c>
       <c r="V30" s="66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.292000000000002</v>
       </c>
       <c r="W30" s="147"/>
@@ -4338,7 +4368,7 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="179"/>
+      <c r="B31" s="185"/>
       <c r="C31" s="108" t="s">
         <v>193</v>
       </c>
@@ -4394,14 +4424,14 @@
         <v>0.17</v>
       </c>
       <c r="T31" s="70">
-        <f t="shared" si="3"/>
+        <f>S31*K31</f>
         <v>178.5</v>
       </c>
       <c r="U31" s="66">
         <v>0.17</v>
       </c>
       <c r="V31" s="135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>357</v>
       </c>
       <c r="W31" s="153"/>
@@ -4411,7 +4441,7 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="179"/>
+      <c r="B32" s="185"/>
       <c r="C32" s="116" t="s">
         <v>199</v>
       </c>
@@ -4481,7 +4511,7 @@
       <c r="A33" s="30">
         <v>31</v>
       </c>
-      <c r="B33" s="180"/>
+      <c r="B33" s="186"/>
       <c r="C33" s="118" t="s">
         <v>202</v>
       </c>
@@ -4557,24 +4587,24 @@
       <c r="J34" s="32"/>
       <c r="K34" s="32"/>
       <c r="L34" s="32"/>
-      <c r="M34" s="176" t="s">
+      <c r="M34" s="182" t="s">
         <v>205</v>
       </c>
-      <c r="N34" s="176"/>
-      <c r="O34" s="176"/>
-      <c r="P34" s="176"/>
+      <c r="N34" s="182"/>
+      <c r="O34" s="182"/>
+      <c r="P34" s="182"/>
       <c r="R34" s="64">
         <f>SUM(R3:R31)</f>
-        <v>670.27689999999996</v>
+        <v>263.07690000000002</v>
       </c>
       <c r="T34" s="132">
-        <f>SUM(T3:T33)</f>
-        <v>5859.5409999999993</v>
+        <f>SUM(T3:T31)</f>
+        <v>5797.701</v>
       </c>
       <c r="U34" s="127"/>
       <c r="V34" s="127">
-        <f>SUM(V3:V33)</f>
-        <v>11661.266</v>
+        <f>SUM(V3:V31)</f>
+        <v>11562.876</v>
       </c>
       <c r="W34" s="32"/>
       <c r="X34" s="67"/>
@@ -4591,34 +4621,70 @@
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
       <c r="L35" s="32"/>
-      <c r="M35" s="177" t="s">
+      <c r="M35" s="183" t="s">
         <v>206</v>
       </c>
-      <c r="N35" s="177"/>
-      <c r="O35" s="177"/>
-      <c r="P35" s="177"/>
+      <c r="N35" s="183"/>
+      <c r="O35" s="183"/>
+      <c r="P35" s="183"/>
       <c r="T35" s="130">
         <f>T34/500</f>
-        <v>11.719081999999998</v>
+        <v>11.595402</v>
       </c>
       <c r="U35" s="128"/>
       <c r="V35" s="131">
         <f>V34/1000</f>
-        <v>11.661265999999999</v>
+        <v>11.562876000000001</v>
       </c>
       <c r="W35" s="32"/>
       <c r="X35" s="67"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" ht="15.75" thickBot="1">
       <c r="A36"/>
       <c r="X36" s="67"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" ht="16.5" thickBot="1">
       <c r="A37"/>
+      <c r="M37" s="173"/>
+      <c r="N37" s="174" t="s">
+        <v>219</v>
+      </c>
+      <c r="O37" s="175"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="175"/>
+      <c r="R37" s="175"/>
+      <c r="S37" s="175"/>
+      <c r="T37" s="175">
+        <f>45.51+16.15</f>
+        <v>61.66</v>
+      </c>
+      <c r="U37" s="175"/>
+      <c r="V37" s="176">
+        <f>69.48+29.36</f>
+        <v>98.84</v>
+      </c>
       <c r="X37" s="67"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" ht="16.5" thickBot="1">
       <c r="A38"/>
+      <c r="M38" s="173"/>
+      <c r="N38" s="174" t="s">
+        <v>220</v>
+      </c>
+      <c r="O38" s="175"/>
+      <c r="P38" s="175"/>
+      <c r="Q38" s="175"/>
+      <c r="R38" s="175"/>
+      <c r="S38" s="175"/>
+      <c r="T38" s="177">
+        <f>T37+T34</f>
+        <v>5859.3609999999999</v>
+      </c>
+      <c r="U38" s="175"/>
+      <c r="V38" s="178">
+        <f>V37+V34</f>
+        <v>11661.716</v>
+      </c>
       <c r="X38" s="67"/>
     </row>
     <row r="39" spans="1:24">
@@ -4927,32 +4993,32 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P8" r:id="rId1"/>
-    <hyperlink ref="P9" r:id="rId2"/>
-    <hyperlink ref="P10" r:id="rId3"/>
-    <hyperlink ref="P11" r:id="rId4"/>
-    <hyperlink ref="P12" r:id="rId5"/>
-    <hyperlink ref="P13" r:id="rId6"/>
-    <hyperlink ref="P14" r:id="rId7"/>
-    <hyperlink ref="P17" r:id="rId8"/>
-    <hyperlink ref="P18" r:id="rId9"/>
-    <hyperlink ref="P19" r:id="rId10"/>
-    <hyperlink ref="P20" r:id="rId11"/>
-    <hyperlink ref="P22" r:id="rId12"/>
-    <hyperlink ref="P23" r:id="rId13"/>
-    <hyperlink ref="P25" r:id="rId14"/>
-    <hyperlink ref="P26" r:id="rId15"/>
-    <hyperlink ref="P6" r:id="rId16"/>
-    <hyperlink ref="P7" r:id="rId17"/>
-    <hyperlink ref="P21" r:id="rId18"/>
-    <hyperlink ref="P3" r:id="rId19"/>
-    <hyperlink ref="P4" r:id="rId20"/>
-    <hyperlink ref="P5" r:id="rId21"/>
-    <hyperlink ref="P27" r:id="rId22"/>
-    <hyperlink ref="P29" r:id="rId23"/>
-    <hyperlink ref="P15" r:id="rId24"/>
-    <hyperlink ref="P30" r:id="rId25"/>
-    <hyperlink ref="P31" r:id="rId26"/>
+    <hyperlink ref="P8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="P10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P11" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="P12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="P13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="P14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="P17" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P18" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="P19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="P22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="P23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="P26" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="P6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="P7" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="P21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P3" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="P4" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="P5" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="P27" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="P29" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="P15" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="P30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="P31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId27"/>
